--- a/tame_output/ON/bt/strategyON_20231130.xlsx
+++ b/tame_output/ON/bt/strategyON_20231130.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-11-28</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>92.5%</t>
+          <t>93.0%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>79.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,12 +776,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-11-28</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-11-28</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.9%</t>
         </is>
       </c>
     </row>
@@ -1069,11 +1069,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-11-28</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>97.4%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-11-28</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.4%</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-11-28</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>125.7%</t>
+          <t>125.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>28.1%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1796"/>
+  <dimension ref="A1:G1797"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42818,7 +42818,7 @@
         <v>45258</v>
       </c>
       <c r="B1796" t="n">
-        <v>3.160927146430493</v>
+        <v>3.162269743666732</v>
       </c>
       <c r="C1796" t="n">
         <v>3.079594415968698</v>
@@ -42834,6 +42834,29 @@
       </c>
       <c r="G1796" t="n">
         <v>4.390948499316334</v>
+      </c>
+    </row>
+    <row r="1797">
+      <c r="A1797" s="2" t="n">
+        <v>45259</v>
+      </c>
+      <c r="B1797" t="n">
+        <v>3.165137517617179</v>
+      </c>
+      <c r="C1797" t="n">
+        <v>3.079532703829831</v>
+      </c>
+      <c r="D1797" t="n">
+        <v>1.56294751687017</v>
+      </c>
+      <c r="E1797" t="n">
+        <v>3.704355286264152</v>
+      </c>
+      <c r="F1797" t="n">
+        <v>2.187088571437823</v>
+      </c>
+      <c r="G1797" t="n">
+        <v>4.391785846692527</v>
       </c>
     </row>
   </sheetData>
